--- a/tables/Smoking_Tier1_HedgesG.xlsx
+++ b/tables/Smoking_Tier1_HedgesG.xlsx
@@ -496,14 +496,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Johnson MW 2026</t>
+          <t>Garcia-Romeu 2015</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="C2" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -512,54 +512,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Odds ratio</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
+          <t>Abstinence rate (%)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12/15 (80%)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OR=6.12 favours psilocybin; Hasselblad-Hedges approximation</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.9987665296646921</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.9893737409844598</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.05474914877652186</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.2339853601756355</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.5307624350402143</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.447985046928705</v>
-      </c>
+          <t>Predictive analysis (quitters vs non-quitters on SOCQ); not a treatment vs control effect size</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Garcia-Romeu 2015</t>
+          <t>Johnson 2014</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -571,12 +557,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Group means (quitters vs non-quitters)</t>
+          <t>Abstinence rate (%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.8 vs 52.1</t>
+          <t>12/15 (80%)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -587,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Predictive analysis (quitters vs non-quitters on SOCQ); not a treatment vs control effect size</t>
+          <t>Single-arm abstinence rate; no comparator</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -619,8 +605,10 @@
           <t>Abstinence rate (%)</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>60</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9/15 (60%)</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -643,14 +631,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Johnson 2014</t>
+          <t>Johnson MW 2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -659,29 +647,45 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
+          <t>Odds ratio</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>6.12</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Single-arm abstinence rate; no comparator</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>Directly reported OR = 6.12 (95% CI, 1.99-23.26; P = .003) from binary logistic regression for the a priori primary outcome (6-month biochemically verified prolonged abstinence), ITT N = 82. Independently recomputed from the reported 2x2 cell counts (17/42 psilocybin abstinent vs 4/40 nicotine-patch abstinent: OR = (17x36)/(25x4) = 6.12), which matches the reported value exactly, supporting a clean conversion with no assumption required.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9987665296646921</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9893737409844598</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.05474914877652186</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2339853601756355</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5307624350402143</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.447985046928705</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
